--- a/public/professeurs-model.xlsx
+++ b/public/professeurs-model.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Nom</t>
   </si>
@@ -41,28 +41,16 @@
     <t>GOGO</t>
   </si>
   <si>
-    <t>Parent 1</t>
-  </si>
-  <si>
-    <t>parent1@gmail.com</t>
-  </si>
-  <si>
-    <t>Parent 2</t>
-  </si>
-  <si>
-    <t>Parent 3</t>
-  </si>
-  <si>
-    <t>Parent 4</t>
-  </si>
-  <si>
-    <t>parent2@gmail.com</t>
-  </si>
-  <si>
-    <t>parent3@gmail.com</t>
-  </si>
-  <si>
-    <t>parent4@gmail.com</t>
+    <t>Prof 1</t>
+  </si>
+  <si>
+    <t>Prof 2</t>
+  </si>
+  <si>
+    <t>prof1@gmail.com</t>
+  </si>
+  <si>
+    <t>prof2@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -125,10 +113,10 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -153,13 +141,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau1" displayName="Tableau1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau1" displayName="Tableau1" ref="A1:D3" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D3"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Nom" dataDxfId="3"/>
     <tableColumn id="2" name="Prénom" dataDxfId="2"/>
-    <tableColumn id="3" name="Email" dataDxfId="0" dataCellStyle="Lien hypertexte"/>
-    <tableColumn id="4" name="Télephone" dataDxfId="1"/>
+    <tableColumn id="3" name="Email" dataDxfId="1" dataCellStyle="Lien hypertexte"/>
+    <tableColumn id="4" name="Télephone" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -428,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.90625" style="1"/>
@@ -459,7 +447,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>22956854397</v>
@@ -470,54 +458,24 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3">
         <v>22956854398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3">
-        <v>22956854399</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3">
-        <v>22956854400</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1"/>
     <hyperlink ref="C2" r:id="rId2"/>
-    <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>